--- a/data/mini-example-resilience/Power_Storage.xlsx
+++ b/data/mini-example-resilience/Power_Storage.xlsx
@@ -5,17 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\Mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9A9D56-BD6A-4C74-8D41-35324ABA83AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740EFCAA-810F-4527-B6C4-C18E45039F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1394,11 +1407,13 @@
         <v>0</v>
       </c>
       <c r="G8" s="14">
-        <v>50</v>
-      </c>
-      <c r="H8" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
       <c r="I8" s="14">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="J8" s="15">
         <v>0.95</v>
@@ -1417,15 +1432,17 @@
       </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
-      <c r="Q8" s="13"/>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
       <c r="R8" s="15">
         <v>4</v>
       </c>
       <c r="S8" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="U8" s="15">
         <v>3821.0756000000001</v>

--- a/data/mini-example-resilience/Power_Storage.xlsx
+++ b/data/mini-example-resilience/Power_Storage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740EFCAA-810F-4527-B6C4-C18E45039F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96C6AE4-695E-42EE-9969-B47103F81902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="15">
         <v>0.95</v>
@@ -1431,7 +1431,9 @@
         <v>0</v>
       </c>
       <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
+      <c r="P8" s="15">
+        <v>0.5</v>
+      </c>
       <c r="Q8" s="13">
         <v>0</v>
       </c>
